--- a/elee201_hw_answers_complete.xlsx
+++ b/elee201_hw_answers_complete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grovecitycollege-my.sharepoint.com/personal/rumbaughlk_gcc_edu/Documents/Documents/Teaching/Linear Circuits/Homework/HW Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{DB5B9418-8ABB-46C3-B5E0-9B2F68BAB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFCE75F3-A89A-4AE9-BC70-9E5629D14B24}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{DB5B9418-8ABB-46C3-B5E0-9B2F68BAB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E57E37A-5390-4503-A6BC-6C2E5A8EA579}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
   </bookViews>
   <sheets>
     <sheet name="HW2" sheetId="7" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="273">
   <si>
     <t>Problem</t>
   </si>
@@ -262,9 +262,6 @@
   </si>
   <si>
     <t>ISC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HW </t>
   </si>
   <si>
     <t>Answer 6</t>
@@ -1848,6 +1845,18 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1877,18 +1886,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2259,42 +2256,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -2378,78 +2375,78 @@
         <v>1.3</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="27">
         <v>4200000</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="47">
         <f>ABS(C3)*10%</f>
         <v>420000</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G3" s="27">
         <v>21600000000</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I3" s="47">
         <f>ABS(G3)*10%</f>
         <v>2160000000</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K3" s="27">
         <v>4.1999999999999997E-3</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M3" s="27">
         <f>ABS(K3)*10%</f>
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O3" s="27">
         <v>1.7499999999999999E-7</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q3" s="27">
         <f>ABS(O3)*10%</f>
         <v>1.7500000000000001E-8</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S3" s="81">
         <v>0.17499999999999999</v>
       </c>
       <c r="T3" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U3" s="27">
         <f>ABS(S3)*10%</f>
         <v>1.7499999999999998E-2</v>
       </c>
       <c r="V3" s="56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W3" s="27">
         <v>1.2000000000000001E-11</v>
       </c>
       <c r="X3" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y3" s="57">
         <f>ABS(W3)*10%</f>
@@ -2461,78 +2458,78 @@
         <v>1.4</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C4" s="27">
         <v>26300</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" s="47">
         <f>ABS(C4)*10%</f>
         <v>2630</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G4" s="27">
         <v>1.6299999999999999E-2</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="47">
         <f>ABS(G4)*10%</f>
         <v>1.6299999999999999E-3</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K4" s="82">
         <v>4</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M4" s="27">
         <f>ABS(K4)*10%</f>
         <v>0.4</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O4" s="27">
         <v>4.3E-3</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="27">
         <f>ABS(O4)*10%</f>
         <v>4.3000000000000004E-4</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S4" s="82">
         <v>36</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U4" s="27">
         <f>ABS(S4)*10%</f>
         <v>3.6</v>
       </c>
       <c r="V4" s="56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W4" s="82">
         <v>40</v>
       </c>
       <c r="X4" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y4" s="57">
         <f>ABS(W4)*10%</f>
@@ -2668,42 +2665,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -2784,24 +2781,24 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B3" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>90</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>91</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="71"/>
       <c r="F3" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" s="23">
         <v>180</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I3" s="71">
         <v>5</v>
@@ -2825,10 +2822,10 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="23">
         <v>0.4</v>
@@ -2987,42 +2984,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -3103,13 +3100,13 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>12</v>
@@ -3138,20 +3135,20 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B4" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>93</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>94</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="71"/>
       <c r="F4" s="46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="23">
         <v>-1.8</v>
@@ -3163,7 +3160,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="23">
         <v>3</v>
@@ -3316,42 +3313,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -3432,13 +3429,13 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B3" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>97</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>98</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="71"/>
@@ -3465,13 +3462,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B4" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>99</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>100</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>12</v>
@@ -3500,10 +3497,10 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="23">
         <v>12</v>
@@ -3515,13 +3512,13 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="23">
+        <v>2</v>
+      </c>
+      <c r="H5" s="23" t="s">
         <v>102</v>
-      </c>
-      <c r="G5" s="23">
-        <v>2</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>103</v>
       </c>
       <c r="I5" s="71">
         <v>0.1</v>
@@ -3545,37 +3542,37 @@
     </row>
     <row r="6" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B6" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>104</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>105</v>
       </c>
       <c r="D6" s="28"/>
       <c r="E6" s="72"/>
       <c r="F6" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="24" t="s">
         <v>106</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>107</v>
       </c>
       <c r="H6" s="24"/>
       <c r="I6" s="72"/>
       <c r="J6" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="K6" s="24" t="s">
         <v>108</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>109</v>
       </c>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="O6" s="24" t="s">
         <v>110</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>111</v>
       </c>
       <c r="P6" s="24"/>
       <c r="Q6" s="24"/>
@@ -3590,29 +3587,29 @@
     </row>
     <row r="7" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="75" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="78"/>
       <c r="F7" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="52" t="s">
         <v>113</v>
-      </c>
-      <c r="G7" s="52" t="s">
-        <v>114</v>
       </c>
       <c r="H7" s="52"/>
       <c r="I7" s="78"/>
       <c r="J7" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" s="32" t="s">
         <v>115</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>116</v>
       </c>
       <c r="L7" s="32"/>
       <c r="M7" s="79"/>
@@ -3631,7 +3628,7 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="76" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3708,42 +3705,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -3824,13 +3821,13 @@
     </row>
     <row r="3" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B3" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>118</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>29</v>
@@ -3859,10 +3856,10 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="23">
         <v>7.5</v>
@@ -3874,7 +3871,7 @@
         <v>0.25</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G4" s="23">
         <v>1.5</v>
@@ -3886,7 +3883,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K4" s="23">
         <v>0.5</v>
@@ -3912,10 +3909,10 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="23">
         <v>20</v>
@@ -3927,7 +3924,7 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" s="23">
         <v>12</v>
@@ -3939,7 +3936,7 @@
         <v>0.25</v>
       </c>
       <c r="J5" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K5" s="23">
         <v>0</v>
@@ -3951,7 +3948,7 @@
         <v>0.05</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O5" s="23">
         <v>2</v>
@@ -4081,50 +4078,50 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
       <c r="Z1" s="97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA1" s="98"/>
       <c r="AB1" s="98"/>
       <c r="AC1" s="99"/>
       <c r="AD1" s="97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AE1" s="98"/>
       <c r="AF1" s="98"/>
@@ -4233,10 +4230,10 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="23">
         <v>0</v>
@@ -4248,7 +4245,7 @@
         <v>0.01</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G3" s="23">
         <v>0</v>
@@ -4260,7 +4257,7 @@
         <v>0.01</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K3" s="23">
         <v>0</v>
@@ -4272,7 +4269,7 @@
         <v>0.01</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O3" s="23">
         <v>0</v>
@@ -4284,7 +4281,7 @@
         <v>0.01</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S3" s="23">
         <v>0</v>
@@ -4296,7 +4293,7 @@
         <v>0.01</v>
       </c>
       <c r="V3" s="56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="W3" s="23">
         <v>8</v>
@@ -4308,19 +4305,19 @@
         <v>0.25</v>
       </c>
       <c r="Z3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA3" t="s">
         <v>132</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>133</v>
       </c>
       <c r="AB3" t="s">
         <v>12</v>
       </c>
       <c r="AD3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE3" t="s">
         <v>134</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>135</v>
       </c>
       <c r="AF3" t="s">
         <v>29</v>
@@ -4328,10 +4325,10 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="23">
         <v>0</v>
@@ -4510,62 +4507,62 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
       <c r="Z1" s="97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA1" s="98"/>
       <c r="AB1" s="98"/>
       <c r="AC1" s="99"/>
       <c r="AD1" s="97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AE1" s="98"/>
       <c r="AF1" s="98"/>
       <c r="AG1" s="99"/>
       <c r="AH1" s="97" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AI1" s="98"/>
       <c r="AJ1" s="98"/>
       <c r="AK1" s="99"/>
       <c r="AL1" s="97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AM1" s="98"/>
       <c r="AN1" s="98"/>
@@ -4698,10 +4695,10 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="23">
         <v>0</v>
@@ -4713,7 +4710,7 @@
         <v>0.01</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G3" s="23">
         <v>0</v>
@@ -4725,7 +4722,7 @@
         <v>0.01</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K3" s="23">
         <v>0</v>
@@ -4737,7 +4734,7 @@
         <v>0.01</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O3" s="23">
         <v>8</v>
@@ -4749,7 +4746,7 @@
         <v>0.25</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S3" s="23">
         <v>0.4</v>
@@ -4761,7 +4758,7 @@
         <v>0.05</v>
       </c>
       <c r="V3" s="56" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W3" s="23">
         <v>0</v>
@@ -4785,31 +4782,31 @@
         <v>0.5</v>
       </c>
       <c r="AD3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AE3">
         <v>0.01</v>
       </c>
       <c r="AF3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG3">
         <v>1E-3</v>
       </c>
       <c r="AH3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI3" t="s">
         <v>144</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>145</v>
       </c>
       <c r="AJ3" t="s">
         <v>11</v>
       </c>
       <c r="AL3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM3" t="s">
         <v>146</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>147</v>
       </c>
       <c r="AN3" t="s">
         <v>12</v>
@@ -4817,13 +4814,13 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>11</v>
@@ -4983,42 +4980,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -5099,13 +5096,13 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B3" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>150</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>12</v>
@@ -5134,13 +5131,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>12</v>
@@ -5169,7 +5166,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>38</v>
@@ -5184,13 +5181,13 @@
         <v>5</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G5" s="23">
         <v>0.05</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I5" s="71">
         <v>2E-3</v>
@@ -5314,42 +5311,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -5430,64 +5427,64 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C3" s="23">
         <v>50</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="71">
         <v>2.5</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G3" s="23">
         <v>1</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I3" s="71">
         <v>0.05</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K3" s="23">
         <v>2</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M3" s="23">
         <v>0.1</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O3" s="23">
         <v>4</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q3" s="23">
         <v>0.1</v>
       </c>
       <c r="R3" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S3" s="23">
         <v>8</v>
       </c>
       <c r="T3" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U3" s="23">
         <v>0.25</v>
@@ -5499,52 +5496,52 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="23">
         <v>100</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4" s="71">
         <v>5</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G4" s="23">
         <v>2</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I4" s="71">
         <v>0.1</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K4" s="23">
         <v>5</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M4" s="23">
         <v>0.1</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O4" s="23">
         <v>10</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q4" s="23">
         <v>0.25</v>
@@ -5685,42 +5682,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -5801,10 +5798,10 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C3" s="23">
         <v>0.2</v>
@@ -5816,31 +5813,31 @@
         <v>0.01</v>
       </c>
       <c r="F3" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="23">
+        <v>3</v>
+      </c>
+      <c r="H3" s="23" t="s">
         <v>160</v>
-      </c>
-      <c r="G3" s="23">
-        <v>3</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>161</v>
       </c>
       <c r="I3" s="71">
         <v>0.05</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K3" s="23">
         <v>-120</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M3" s="23">
         <v>1</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O3" s="23">
         <v>0.19600000000000001</v>
@@ -5862,20 +5859,20 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="71"/>
       <c r="F4" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G4" s="23">
         <v>4</v>
@@ -5887,37 +5884,37 @@
         <v>0.1</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K4" s="23">
         <v>4</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="23">
         <v>0.05</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O4" s="23">
         <v>0.25</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="23">
         <v>0.01</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S4" s="23">
         <v>45</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U4" s="23">
         <v>1</v>
@@ -5929,24 +5926,24 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B5" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>169</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>170</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="71"/>
       <c r="F5" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G5" s="23">
         <v>0.111111</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I5" s="71">
         <v>0.01</v>
@@ -6074,44 +6071,44 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
       <c r="Z1" s="97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA1" s="98"/>
       <c r="AB1" s="98"/>
@@ -6208,85 +6205,85 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B3" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>172</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>173</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="71"/>
       <c r="F3" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>174</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>175</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="71"/>
       <c r="J3" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="K3" s="23" t="s">
         <v>176</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>177</v>
       </c>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
       <c r="N3" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="O3" s="23" t="s">
         <v>178</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>179</v>
       </c>
       <c r="P3" s="23"/>
       <c r="Q3" s="23"/>
       <c r="R3" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="T3" s="23"/>
       <c r="U3" s="23"/>
       <c r="V3" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="W3" s="23" t="s">
         <v>181</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>182</v>
       </c>
       <c r="X3" s="23"/>
       <c r="Y3" s="73"/>
       <c r="Z3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA3" t="s">
         <v>183</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B4" s="46" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="71"/>
       <c r="F4" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>186</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>187</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="71"/>
       <c r="J4" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K4" s="23">
         <v>1</v>
@@ -6296,18 +6293,18 @@
         <v>0.05</v>
       </c>
       <c r="N4" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="O4" s="23" t="s">
         <v>188</v>
-      </c>
-      <c r="O4" s="23" t="s">
-        <v>189</v>
       </c>
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="S4" s="23" t="s">
         <v>190</v>
-      </c>
-      <c r="S4" s="23" t="s">
-        <v>191</v>
       </c>
       <c r="T4" s="23"/>
       <c r="U4" s="23"/>
@@ -6318,13 +6315,13 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" s="31" t="s">
         <v>12</v>
@@ -6334,17 +6331,17 @@
         <v>14</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="71"/>
       <c r="J5" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="K5" s="23" t="s">
         <v>194</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>195</v>
       </c>
       <c r="L5" s="23" t="s">
         <v>12</v>
@@ -6365,13 +6362,13 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B6" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>196</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>197</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>29</v>
@@ -6442,34 +6439,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25AE21B6-565E-4D2D-AF85-3C3B920C40A1}">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.54296875" customWidth="1"/>
     <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="93" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -6562,7 +6560,9 @@
       <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="6">
+        <v>0.1</v>
+      </c>
       <c r="J4" s="15"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -6605,7 +6605,9 @@
       <c r="L5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13">
@@ -6646,11 +6648,6 @@
       </c>
       <c r="M6" s="9">
         <v>0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E20" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6705,50 +6702,50 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
       <c r="Z1" s="97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA1" s="98"/>
       <c r="AB1" s="98"/>
       <c r="AC1" s="99"/>
       <c r="AD1" s="97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AE1" s="98"/>
       <c r="AF1" s="98"/>
@@ -6857,10 +6854,10 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="23">
         <v>3</v>
@@ -6872,20 +6869,20 @@
         <v>0.1</v>
       </c>
       <c r="F3" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>199</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>200</v>
       </c>
       <c r="H3" s="23" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="71"/>
       <c r="J3" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="K3" s="23" t="s">
         <v>201</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="L3" s="23" t="s">
         <v>20</v>
@@ -6895,27 +6892,27 @@
         <v>56</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P3" s="23" t="s">
         <v>12</v>
       </c>
       <c r="Q3" s="23"/>
       <c r="R3" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="S3" s="23" t="s">
         <v>204</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>205</v>
       </c>
       <c r="T3" s="23" t="s">
         <v>20</v>
       </c>
       <c r="U3" s="23"/>
       <c r="V3" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="W3" s="23" t="s">
         <v>206</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>207</v>
       </c>
       <c r="X3" s="23" t="s">
         <v>12</v>
@@ -6934,13 +6931,13 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE3">
         <v>0.57999999999999996</v>
       </c>
       <c r="AF3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG3">
         <v>0.03</v>
@@ -6948,7 +6945,7 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="46" t="s">
         <v>56</v>
@@ -6963,7 +6960,7 @@
         <v>0.25</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G4" s="23">
         <v>0</v>
@@ -7122,42 +7119,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -7238,13 +7235,13 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B3" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>208</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>209</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>11</v>
@@ -7273,13 +7270,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>11</v>
@@ -7435,42 +7432,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -7551,16 +7548,16 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" s="23">
         <v>20000</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E3" s="71">
         <v>200</v>
@@ -7588,16 +7585,16 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C4" s="23">
         <v>10000</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E4" s="71">
         <v>100</v>
@@ -7625,24 +7622,24 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B5" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>213</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>214</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="71"/>
       <c r="F5" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="23" t="s">
         <v>211</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>212</v>
       </c>
       <c r="I5" s="71"/>
       <c r="J5" s="35"/>
@@ -7772,50 +7769,50 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
       <c r="Z1" s="97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA1" s="98"/>
       <c r="AB1" s="98"/>
       <c r="AC1" s="99"/>
       <c r="AD1" s="97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AE1" s="98"/>
       <c r="AF1" s="98"/>
@@ -7924,22 +7921,22 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" s="23">
         <v>10000</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E3" s="71">
         <v>100</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G3" s="23">
         <v>40</v>
@@ -7949,63 +7946,63 @@
         <v>1</v>
       </c>
       <c r="J3" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K3" s="23">
         <v>9875</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M3" s="23">
         <v>100</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O3" s="23">
         <v>10125</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q3" s="23">
         <v>100</v>
       </c>
       <c r="R3" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="S3" s="23" t="s">
         <v>219</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>220</v>
       </c>
       <c r="T3" s="23"/>
       <c r="U3" s="23"/>
       <c r="V3" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W3" s="23">
         <v>40</v>
       </c>
       <c r="X3" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y3" s="73">
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA3">
         <v>0.25</v>
       </c>
       <c r="AB3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AC3">
         <v>0.01</v>
       </c>
       <c r="AD3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AE3">
         <v>80</v>
@@ -8016,22 +8013,22 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C4" s="23">
         <v>500</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E4" s="71">
         <v>5</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G4" s="23">
         <v>20</v>
@@ -8041,37 +8038,37 @@
         <v>0.5</v>
       </c>
       <c r="J4" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K4" s="23">
         <v>25</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M4" s="23">
         <v>1</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O4" s="23">
         <v>487.5</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q4" s="23">
         <v>5</v>
       </c>
       <c r="R4" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S4" s="23">
         <v>512.5</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="U4" s="23">
         <v>5</v>
@@ -8083,28 +8080,28 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C5" s="23">
         <v>10</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E5" s="71">
         <v>0.25</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G5" s="23">
         <v>0.16</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I5" s="71">
         <v>0.01</v>
@@ -8116,7 +8113,7 @@
         <v>25</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M5" s="23">
         <v>0.5</v>
@@ -8216,30 +8213,30 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="93" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="96" t="s">
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="95"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="85"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -8539,24 +8536,24 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="93" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -8745,24 +8742,24 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="96" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -8986,36 +8983,36 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="96" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="96" t="s">
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="96" t="s">
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="95"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="84"/>
+      <c r="U1" s="85"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -9307,30 +9304,30 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="96" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="96" t="s">
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="95"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="85"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -9570,24 +9567,24 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="96" t="s">
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="96" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="95"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="85"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -9672,7 +9669,7 @@
         <v>0.25</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="65">
         <v>1.53</v>
@@ -9693,13 +9690,13 @@
         <v>3.83</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="65">
         <v>2.09</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="66">
         <v>0.1</v>
@@ -9802,42 +9799,42 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="38"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="86" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="89" t="s">
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="92" t="s">
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="85"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="89"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
@@ -9918,10 +9915,10 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="23">
         <v>-10</v>
@@ -9955,16 +9952,16 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B4" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>84</v>
       </c>
       <c r="E4" s="71"/>
       <c r="F4" s="46"/>
@@ -9990,18 +9987,18 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B5" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="71"/>
       <c r="F5" s="46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" s="23">
         <v>1</v>
@@ -10029,16 +10026,16 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="70" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="24">
         <v>16</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" s="72">
         <v>0.5</v>
